--- a/data/202603_인프런_매출 정산 변환.xlsx
+++ b/data/202603_인프런_매출 정산 변환.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9511DFB8-6F59-4592-96F0-3D550C1CD6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29100" yWindow="2430" windowWidth="25350" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26775" yWindow="1305" windowWidth="25350" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매출 입력" sheetId="1" r:id="rId1"/>
